--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.37067379962208</v>
+        <v>7.535234492438588</v>
       </c>
       <c r="D2" t="n">
-        <v>36.41771546926029</v>
+        <v>5.917878763754797</v>
       </c>
       <c r="E2" t="n">
-        <v>4.564428629261826</v>
+        <v>0.7417196522550467</v>
       </c>
       <c r="F2" t="n">
-        <v>9.738162670067236</v>
+        <v>1.582451433885926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.24181654109842</v>
+        <v>6.051795187928494</v>
       </c>
       <c r="D3" t="n">
-        <v>16.94139012912581</v>
+        <v>2.752975895982945</v>
       </c>
       <c r="E3" t="n">
-        <v>4.564428629261826</v>
+        <v>0.7417196522550467</v>
       </c>
       <c r="F3" t="n">
-        <v>9.738162670067236</v>
+        <v>1.582451433885926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
